--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_0_13.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_0_13.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>577353.1922805905</v>
+        <v>577357.7000544965</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.244635141</v>
+        <v>925399.3994514379</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422521</v>
+        <v>18327015.93006067</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5475696.932305135</v>
+        <v>5475808.405183962</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -694,28 +694,28 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>241</v>
+        <v>200.3360962888297</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X2" t="n">
-        <v>112.2877629084735</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="3">
@@ -728,25 +728,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
         <v>0.7465913262578567</v>
@@ -782,19 +782,19 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>49.26994054353487</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>14.83685490770588</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J4" t="n">
         <v>93.35918011667277</v>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -889,13 +889,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>230.8744955960827</v>
       </c>
       <c r="E5" t="n">
-        <v>238.7610722963053</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F5" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -965,28 +965,28 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1013,19 +1013,19 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>35.36610207477812</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1083,13 +1083,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1132,19 +1132,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>230.8744955960827</v>
       </c>
       <c r="G8" t="n">
-        <v>114.9170236876542</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H8" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I8" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>145.3912560091964</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>126.358590200387</v>
       </c>
       <c r="E9" t="n">
         <v>157.6450804554009</v>
@@ -1302,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>22.0339917726843</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>44.30348359856712</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>190.3328114308427</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -1402,19 +1402,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y11" t="n">
-        <v>241</v>
+        <v>39.77286532336496</v>
       </c>
     </row>
     <row r="12">
@@ -1439,25 +1439,25 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>157.9784691189487</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1502,10 +1502,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>85.16798613829975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>22.0339917726843</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1557,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>212.2728000000236</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1615,10 +1615,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>200.3360962888296</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1660,10 +1660,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>115.5373440430929</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>3.833957768458675</v>
       </c>
       <c r="J15" t="n">
         <v>0.7465913262578567</v>
@@ -1721,28 +1721,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W15" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>39.82778746869523</v>
+        <v>14.83685490770591</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1840,19 +1840,19 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1882,10 +1882,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>23.81301614990497</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1910,22 +1910,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -1973,13 +1973,13 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>207.0647355219964</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>205.6826957773044</v>
+        <v>181.2921930499176</v>
       </c>
     </row>
     <row r="19">
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2068,25 +2068,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
@@ -2159,10 +2159,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>9.954578461909239</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2201,19 +2201,19 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>146.9140566787055</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2286,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2314,16 +2314,16 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.225708031910471e-11</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2359,10 +2359,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2435,25 +2435,25 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>98.22847700514936</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>111.1339479153803</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2469,58 +2469,58 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2551,16 +2551,16 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2599,16 +2599,16 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>29.75784556612239</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>70.84795259427446</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2669,25 +2669,25 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>212.2853856434421</v>
       </c>
     </row>
     <row r="30">
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>4.525096818297269</v>
+        <v>84.4730545048111</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2909,25 +2909,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -3028,13 +3028,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H32" t="n">
-        <v>212.2728000001191</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3076,16 +3076,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>92.31192385075794</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
         <v>171.6831711038378</v>
@@ -3155,10 +3155,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>104.6829309709404</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3186,52 +3186,52 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3313,16 +3313,16 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="36">
@@ -3389,19 +3389,19 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>50.01653186979276</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>29.79900896488263</v>
       </c>
     </row>
     <row r="37">
@@ -3459,25 +3459,25 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -3493,19 +3493,19 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>220.2131257424249</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3544,10 +3544,10 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3556,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="39">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>157.6450804554009</v>
@@ -3632,13 +3632,13 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X39" t="n">
-        <v>85.25827556447292</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>158.187398751566</v>
       </c>
     </row>
     <row r="40">
@@ -3654,49 +3654,49 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3727,31 +3727,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="F41" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G41" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H41" t="n">
-        <v>190.3328114308427</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3863,19 +3863,19 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>82.33442675869675</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>29.79900896488263</v>
       </c>
     </row>
     <row r="43">
@@ -3927,13 +3927,13 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>44.30348359856712</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3964,22 +3964,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4009,19 +4009,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.37085862661479e-10</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="45">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -4052,13 +4052,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4100,19 +4100,19 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>205.7729852034775</v>
+        <v>122.3079715109942</v>
       </c>
       <c r="Y45" t="n">
-        <v>29.75784556612239</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="46">
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="C2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R2" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S2" t="n">
-        <v>601.4856691642474</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T2" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U2" t="n">
-        <v>376.1363261701753</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V2" t="n">
-        <v>132.7019827358318</v>
+        <v>761.6974622895962</v>
       </c>
       <c r="W2" t="n">
-        <v>132.7019827358318</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="X2" t="n">
-        <v>19.28</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.03413265278571</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C3" t="n">
-        <v>20.03413265278571</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D3" t="n">
-        <v>20.03413265278571</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E3" t="n">
-        <v>20.03413265278571</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F3" t="n">
-        <v>20.03413265278571</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G3" t="n">
-        <v>20.03413265278571</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H3" t="n">
-        <v>20.03413265278571</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I3" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L3" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M3" t="n">
-        <v>234.7819638733197</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N3" t="n">
-        <v>473.3719638733197</v>
+        <v>621.8469951458151</v>
       </c>
       <c r="O3" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U3" t="n">
-        <v>914.2323832893587</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V3" t="n">
-        <v>679.0802750576159</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W3" t="n">
-        <v>435.6459316232725</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X3" t="n">
-        <v>227.7944314177396</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y3" t="n">
-        <v>20.03413265278571</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I4" t="n">
-        <v>136.0766383258138</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J4" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y4" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>728.5590416377008</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C5" t="n">
-        <v>728.5590416377008</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D5" t="n">
-        <v>728.5590416377008</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="E5" t="n">
-        <v>487.3862413384025</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="F5" t="n">
-        <v>243.9518979040591</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="G5" t="n">
-        <v>243.9518979040591</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="H5" t="n">
-        <v>243.9518979040591</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I5" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T5" t="n">
-        <v>728.5590416377008</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U5" t="n">
-        <v>728.5590416377008</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V5" t="n">
-        <v>728.5590416377008</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W5" t="n">
-        <v>728.5590416377008</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X5" t="n">
-        <v>728.5590416377008</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y5" t="n">
-        <v>728.5590416377008</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C6" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D6" t="n">
-        <v>19.28</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E6" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F6" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G6" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H6" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I6" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L6" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M6" t="n">
-        <v>613.1906659261865</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N6" t="n">
-        <v>781.3565223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O6" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P6" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>928.2766645709312</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>726.0900699296972</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U6" t="n">
-        <v>497.8664516660862</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V6" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W6" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X6" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I7" t="n">
-        <v>19.28</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J7" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F8" t="n">
-        <v>591.3940537960203</v>
+        <v>730.8505943024719</v>
       </c>
       <c r="G8" t="n">
-        <v>475.3162520913191</v>
+        <v>487.4018176583718</v>
       </c>
       <c r="H8" t="n">
-        <v>231.8819086569757</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I8" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R8" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y8" t="n">
-        <v>591.3940537960203</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>964</v>
+        <v>795.8418184905681</v>
       </c>
       <c r="C9" t="n">
-        <v>817.1401454452562</v>
+        <v>795.8418184905681</v>
       </c>
       <c r="D9" t="n">
-        <v>668.2057357840049</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E9" t="n">
-        <v>508.9682807785495</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F9" t="n">
-        <v>362.4337228054344</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G9" t="n">
-        <v>223.7028973880499</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H9" t="n">
-        <v>110.3337617956292</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L9" t="n">
-        <v>144.6375600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M9" t="n">
-        <v>383.2275600578374</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="N9" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O9" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P9" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="C10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="D10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="E10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="F10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="G10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="H10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="I10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="J10" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>151.0633604548096</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q10" t="n">
-        <v>64.03099353390618</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="S10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="T10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="U10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="V10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="W10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="X10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="Y10" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>467.0396977630861</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="C11" t="n">
-        <v>467.0396977630861</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="D11" t="n">
-        <v>467.0396977630861</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="E11" t="n">
-        <v>467.0396977630861</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="F11" t="n">
-        <v>223.6053543287427</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="G11" t="n">
-        <v>223.6053543287427</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="H11" t="n">
-        <v>223.6053543287427</v>
+        <v>243.9530410142718</v>
       </c>
       <c r="I11" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R11" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S11" t="n">
-        <v>953.9083846317729</v>
+        <v>752.9257720901863</v>
       </c>
       <c r="T11" t="n">
-        <v>953.9083846317729</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="U11" t="n">
-        <v>710.4740411974295</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="V11" t="n">
-        <v>710.4740411974295</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="W11" t="n">
-        <v>710.4740411974295</v>
+        <v>527.5764290961142</v>
       </c>
       <c r="X11" t="n">
-        <v>710.4740411974295</v>
+        <v>284.1276524520142</v>
       </c>
       <c r="Y11" t="n">
-        <v>467.0396977630861</v>
+        <v>243.9530410142718</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>501.9048939478338</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="C12" t="n">
-        <v>327.4518646667068</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="D12" t="n">
-        <v>178.5174550054555</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="E12" t="n">
-        <v>19.28</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="F12" t="n">
-        <v>19.28</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G12" t="n">
-        <v>19.28</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H12" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L12" t="n">
-        <v>19.28</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M12" t="n">
-        <v>234.7819638733197</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N12" t="n">
-        <v>473.3719638733197</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O12" t="n">
-        <v>711.9619638733197</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P12" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S12" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T12" t="n">
-        <v>964</v>
+        <v>529.8960702829295</v>
       </c>
       <c r="U12" t="n">
-        <v>964</v>
+        <v>529.8960702829295</v>
       </c>
       <c r="V12" t="n">
-        <v>964</v>
+        <v>529.8960702829295</v>
       </c>
       <c r="W12" t="n">
-        <v>964</v>
+        <v>529.8960702829295</v>
       </c>
       <c r="X12" t="n">
-        <v>756.1484997944672</v>
+        <v>529.8960702829295</v>
       </c>
       <c r="Y12" t="n">
-        <v>670.1202309679018</v>
+        <v>529.8960702829295</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="C13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="D13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="E13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="F13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="G13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="H13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="I13" t="n">
-        <v>19.28</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="J13" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="R13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="S13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="T13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="U13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="V13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="W13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="X13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
       <c r="Y13" t="n">
-        <v>153.8122904902707</v>
+        <v>64.03213664411894</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>233.6969696969936</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C14" t="n">
-        <v>233.6969696969936</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D14" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E14" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="F14" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="G14" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="H14" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964.0000000000239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>964.0000000000239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R14" t="n">
-        <v>964.0000000000239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S14" t="n">
-        <v>964.0000000000239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T14" t="n">
-        <v>964.0000000000239</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U14" t="n">
-        <v>964.0000000000239</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V14" t="n">
-        <v>964.0000000000239</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W14" t="n">
-        <v>964.0000000000239</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X14" t="n">
-        <v>720.5656565656805</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y14" t="n">
-        <v>477.131313131337</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>136.7385205751018</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="C15" t="n">
-        <v>20.03413265278571</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="D15" t="n">
-        <v>20.03413265278571</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="E15" t="n">
-        <v>20.03413265278571</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="F15" t="n">
-        <v>20.03413265278571</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="G15" t="n">
-        <v>20.03413265278571</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="H15" t="n">
-        <v>20.03413265278571</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="I15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L15" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M15" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N15" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O15" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P15" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S15" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T15" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U15" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V15" t="n">
-        <v>964</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W15" t="n">
-        <v>720.5656565656566</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="X15" t="n">
-        <v>512.7141563601238</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="Y15" t="n">
-        <v>304.9538575951698</v>
+        <v>23.90796037760316</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="H16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="I16" t="n">
-        <v>113.5822021380533</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J16" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="C17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="D17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="E17" t="n">
-        <v>749.5830303030303</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="F17" t="n">
-        <v>506.1486868686869</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="G17" t="n">
-        <v>262.7143434343434</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="H17" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021275</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R17" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S17" t="n">
-        <v>953.9083846317729</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="T17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="U17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="V17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="W17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="X17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="Y17" t="n">
-        <v>953.9083846317729</v>
+        <v>718.7806050553886</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>165.814557973115</v>
+        <v>612.718391167419</v>
       </c>
       <c r="C18" t="n">
-        <v>165.814557973115</v>
+        <v>612.718391167419</v>
       </c>
       <c r="D18" t="n">
-        <v>165.814557973115</v>
+        <v>463.7839815061678</v>
       </c>
       <c r="E18" t="n">
-        <v>165.814557973115</v>
+        <v>304.5465265007123</v>
       </c>
       <c r="F18" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L18" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M18" t="n">
-        <v>473.3719638733197</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N18" t="n">
-        <v>711.9619638733197</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O18" t="n">
-        <v>711.9619638733197</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P18" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S18" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T18" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U18" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V18" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W18" t="n">
-        <v>581.4263569436018</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X18" t="n">
-        <v>373.5748567380689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y18" t="n">
-        <v>165.814557973115</v>
+        <v>780.9337281874871</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C20" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D20" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E20" t="n">
-        <v>720.5656565656566</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F20" t="n">
-        <v>477.1313131313132</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>233.6969696969697</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>512.7141563601238</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="C21" t="n">
-        <v>338.2611270789968</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="D21" t="n">
-        <v>189.3267174177455</v>
+        <v>464.5381141589534</v>
       </c>
       <c r="E21" t="n">
-        <v>30.08926241229</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F21" t="n">
-        <v>20.03413265278571</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>487.8331058683492</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U21" t="n">
-        <v>964</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="V21" t="n">
-        <v>964</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="W21" t="n">
-        <v>720.5656565656566</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="X21" t="n">
-        <v>512.7141563601238</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="Y21" t="n">
-        <v>512.7141563601238</v>
+        <v>613.4725238202047</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E23" t="n">
-        <v>749.5830303030303</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F23" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G23" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964.000000000073</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="V23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="C24" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M24" t="n">
-        <v>613.1906659261865</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N24" t="n">
-        <v>725.41</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O24" t="n">
-        <v>964</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>790.5826554506689</v>
+        <v>864.836471667051</v>
       </c>
       <c r="U24" t="n">
-        <v>790.5826554506689</v>
+        <v>636.61285340344</v>
       </c>
       <c r="V24" t="n">
-        <v>678.3261424048302</v>
+        <v>401.4607451716973</v>
       </c>
       <c r="W24" t="n">
-        <v>434.8917989704868</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="X24" t="n">
-        <v>227.0402987649539</v>
+        <v>158.0119685275972</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.28</v>
+        <v>158.0119685275972</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="C26" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>710.516763498309</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>467.067986854209</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T26" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U26" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V26" t="n">
-        <v>506.1486868686869</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W26" t="n">
-        <v>262.7143434343434</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X26" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y26" t="n">
-        <v>19.28</v>
+        <v>953.9655401424092</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>49.33842986477009</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="C27" t="n">
-        <v>19.28</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>90.84473158927784</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M27" t="n">
-        <v>374.6006659261865</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N27" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U27" t="n">
-        <v>735.7763817363891</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V27" t="n">
-        <v>500.6242735046464</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="W27" t="n">
-        <v>257.1899300703029</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="X27" t="n">
-        <v>49.33842986477009</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="Y27" t="n">
-        <v>49.33842986477009</v>
+        <v>259.0600686093459</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W28" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F29" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X29" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y29" t="n">
-        <v>720.5656565656566</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23.85080486696694</v>
+        <v>279.0604900729671</v>
       </c>
       <c r="C30" t="n">
-        <v>23.85080486696694</v>
+        <v>104.6074607918401</v>
       </c>
       <c r="D30" t="n">
-        <v>23.85080486696694</v>
+        <v>104.6074607918401</v>
       </c>
       <c r="E30" t="n">
-        <v>23.85080486696694</v>
+        <v>104.6074607918401</v>
       </c>
       <c r="F30" t="n">
-        <v>23.85080486696694</v>
+        <v>104.6074607918401</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M30" t="n">
-        <v>257.87</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N30" t="n">
-        <v>496.46</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O30" t="n">
-        <v>735.0500000000001</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P30" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S30" t="n">
-        <v>689.4131260035546</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T30" t="n">
-        <v>487.2265313623206</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U30" t="n">
-        <v>259.0029130987097</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V30" t="n">
-        <v>23.85080486696694</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="W30" t="n">
-        <v>23.85080486696694</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="X30" t="n">
-        <v>23.85080486696694</v>
+        <v>655.0361258579891</v>
       </c>
       <c r="Y30" t="n">
-        <v>23.85080486696694</v>
+        <v>447.2758270930352</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>720.5656565657769</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C32" t="n">
-        <v>720.5656565657769</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D32" t="n">
-        <v>720.5656565657769</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E32" t="n">
-        <v>720.5656565657769</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F32" t="n">
-        <v>477.1313131314334</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="G32" t="n">
-        <v>233.69696969709</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964.0000000001203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>964.0000000001203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>964.0000000001203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>964.0000000001203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>964.0000000001203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U32" t="n">
-        <v>964.0000000001203</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V32" t="n">
-        <v>964.0000000001203</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W32" t="n">
-        <v>964.0000000001203</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X32" t="n">
-        <v>964.0000000001203</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y32" t="n">
-        <v>720.5656565657769</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>19.28</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="C33" t="n">
-        <v>19.28</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="D33" t="n">
-        <v>19.28</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="E33" t="n">
-        <v>19.28</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="F33" t="n">
-        <v>19.28</v>
+        <v>112.5255106362308</v>
       </c>
       <c r="G33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>304.1765223866491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M33" t="n">
-        <v>542.7665223866492</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N33" t="n">
-        <v>781.3565223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O33" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S33" t="n">
-        <v>790.5826554506689</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T33" t="n">
-        <v>588.3960608094349</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U33" t="n">
-        <v>360.1724425458239</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V33" t="n">
-        <v>125.0203343140812</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="W33" t="n">
-        <v>19.28</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="X33" t="n">
-        <v>19.28</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="Y33" t="n">
-        <v>19.28</v>
+        <v>259.0600686093459</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T34" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y34" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="C35" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="D35" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="E35" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="F35" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="G35" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R35" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S35" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T35" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U35" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V35" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W35" t="n">
-        <v>506.1486868686869</v>
+        <v>710.516763498309</v>
       </c>
       <c r="X35" t="n">
-        <v>506.1486868686869</v>
+        <v>710.516763498309</v>
       </c>
       <c r="Y35" t="n">
-        <v>262.7143434343434</v>
+        <v>467.067986854209</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>249.2431058683491</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M36" t="n">
-        <v>304.1765223866491</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N36" t="n">
-        <v>542.7665223866492</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O36" t="n">
-        <v>781.3565223866492</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P36" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U36" t="n">
-        <v>913.478250636573</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V36" t="n">
-        <v>678.3261424048302</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W36" t="n">
-        <v>434.8917989704868</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X36" t="n">
-        <v>227.0402987649539</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W37" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>710.4740411974295</v>
+        <v>241.7186438601369</v>
       </c>
       <c r="C38" t="n">
-        <v>506.1486868686869</v>
+        <v>241.7186438601369</v>
       </c>
       <c r="D38" t="n">
-        <v>506.1486868686869</v>
+        <v>241.7186438601369</v>
       </c>
       <c r="E38" t="n">
-        <v>262.7143434343434</v>
+        <v>241.7186438601369</v>
       </c>
       <c r="F38" t="n">
-        <v>19.28</v>
+        <v>241.7186438601369</v>
       </c>
       <c r="G38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S38" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T38" t="n">
-        <v>953.9083846317729</v>
+        <v>728.6161971483371</v>
       </c>
       <c r="U38" t="n">
-        <v>953.9083846317729</v>
+        <v>485.167420504237</v>
       </c>
       <c r="V38" t="n">
-        <v>953.9083846317729</v>
+        <v>485.167420504237</v>
       </c>
       <c r="W38" t="n">
-        <v>953.9083846317729</v>
+        <v>485.167420504237</v>
       </c>
       <c r="X38" t="n">
-        <v>710.4740411974295</v>
+        <v>485.167420504237</v>
       </c>
       <c r="Y38" t="n">
-        <v>710.4740411974295</v>
+        <v>241.7186438601369</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>501.9048939478338</v>
+        <v>352.9716273967953</v>
       </c>
       <c r="C39" t="n">
-        <v>327.4518646667068</v>
+        <v>178.5185981156682</v>
       </c>
       <c r="D39" t="n">
-        <v>178.5174550054555</v>
+        <v>178.5185981156682</v>
       </c>
       <c r="E39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>304.1765223866491</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N39" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O39" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W39" t="n">
-        <v>964</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X39" t="n">
-        <v>877.8805297328556</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="Y39" t="n">
-        <v>670.1202309679018</v>
+        <v>352.9716273967953</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>953.9083846317729</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C41" t="n">
-        <v>953.9083846317729</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D41" t="n">
-        <v>710.4740411974295</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E41" t="n">
-        <v>710.4740411974295</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F41" t="n">
-        <v>467.0396977630861</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G41" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I41" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>194.4871619339127</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C42" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D42" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E42" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F42" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G42" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H42" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I42" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L42" t="n">
-        <v>234.7819638733197</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M42" t="n">
-        <v>234.7819638733197</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N42" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O42" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P42" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U42" t="n">
-        <v>880.8339123649528</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V42" t="n">
-        <v>645.6818041332101</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W42" t="n">
-        <v>402.2474606988666</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X42" t="n">
-        <v>402.2474606988666</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y42" t="n">
-        <v>194.4871619339127</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>151.0633604548096</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>64.03099353390618</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C44" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D44" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E44" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="F44" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964.0000000001385</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>964.0000000001385</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R44" t="n">
-        <v>964.0000000001385</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S44" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="T44" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U44" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V44" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W44" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X44" t="n">
-        <v>749.5830303030303</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y44" t="n">
-        <v>749.5830303030303</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>19.28</v>
+        <v>464.5381141589534</v>
       </c>
       <c r="C45" t="n">
-        <v>19.28</v>
+        <v>464.5381141589534</v>
       </c>
       <c r="D45" t="n">
-        <v>19.28</v>
+        <v>464.5381141589534</v>
       </c>
       <c r="E45" t="n">
-        <v>19.28</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F45" t="n">
-        <v>19.28</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G45" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H45" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I45" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L45" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M45" t="n">
-        <v>542.7665223866492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N45" t="n">
-        <v>542.7665223866492</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O45" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U45" t="n">
-        <v>735.7763817363891</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V45" t="n">
-        <v>500.6242735046464</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W45" t="n">
-        <v>257.1899300703029</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X45" t="n">
-        <v>49.33842986477009</v>
+        <v>840.5137499439754</v>
       </c>
       <c r="Y45" t="n">
-        <v>19.28</v>
+        <v>632.7534511790215</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C46" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D46" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E46" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F46" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G46" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H46" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I46" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J46" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K46" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L46" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M46" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N46" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O46" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P46" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q46" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R46" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S46" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T46" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U46" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V46" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W46" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X46" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y46" t="n">
-        <v>829.4677095097293</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
   </sheetData>
@@ -7959,7 +7959,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K2" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L2" t="n">
         <v>417.6612145504504</v>
@@ -7974,7 +7974,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P2" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q2" t="n">
         <v>212.3149906599047</v>
@@ -8044,13 +8044,13 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M3" t="n">
-        <v>233.1889872709904</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N3" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O3" t="n">
-        <v>383.5962444444444</v>
+        <v>233.6791982203443</v>
       </c>
       <c r="P3" t="n">
         <v>318.4627686399372</v>
@@ -8196,7 +8196,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L5" t="n">
         <v>417.6612145504504</v>
@@ -8281,19 +8281,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M6" t="n">
-        <v>383.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N6" t="n">
-        <v>301.2062135585481</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P6" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R6" t="n">
         <v>45.52166981132082</v>
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L8" t="n">
         <v>417.6612145504504</v>
@@ -8515,16 +8515,16 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L9" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M9" t="n">
-        <v>383.1340339220183</v>
+        <v>241.9453110519923</v>
       </c>
       <c r="N9" t="n">
-        <v>222.3966654323053</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P9" t="n">
         <v>318.4627686399372</v>
@@ -8670,7 +8670,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L11" t="n">
         <v>417.6612145504504</v>
@@ -8749,22 +8749,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M12" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N12" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O12" t="n">
-        <v>383.5962444444444</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P12" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
         <v>210.0772877358491</v>
@@ -8922,7 +8922,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P14" t="n">
-        <v>321.7421299892608</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8992,19 +8992,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M15" t="n">
-        <v>241.9030217474054</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P15" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q15" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9144,7 +9144,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L17" t="n">
         <v>417.6612145504504</v>
@@ -9229,16 +9229,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M18" t="n">
-        <v>368.526819785625</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N18" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>312.5053919605859</v>
       </c>
       <c r="P18" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
         <v>210.0772877358491</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,19 +9466,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>186.8300115967677</v>
+        <v>357.7767872515269</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9633,7 +9633,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P23" t="n">
-        <v>321.7421299893105</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q23" t="n">
         <v>212.3149906599047</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N24" t="n">
-        <v>244.694574784155</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9934,19 +9934,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>301.2062135585481</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10177,16 +10177,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
-        <v>295.1415200271288</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
         <v>210.0772877358491</v>
@@ -10344,7 +10344,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>321.7421299893582</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,19 +10408,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>299.7048467786739</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>383.1340339220183</v>
+        <v>197.6503338623806</v>
       </c>
       <c r="N33" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
@@ -10566,7 +10566,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
@@ -10648,22 +10648,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
-        <v>318.4627686399372</v>
+        <v>295.1552315763977</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10888,13 +10888,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>197.6223334354527</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N39" t="n">
-        <v>372.3417120833333</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
@@ -11043,7 +11043,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
         <v>449.5135334928325</v>
@@ -11119,25 +11119,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>229.6093331288462</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>197.6503338623806</v>
       </c>
       <c r="N42" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O42" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11292,7 +11292,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P44" t="n">
-        <v>321.7421299893766</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q44" t="n">
         <v>212.3149906599047</v>
@@ -11356,19 +11356,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M45" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N45" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>198.1125443848066</v>
       </c>
       <c r="P45" t="n">
         <v>318.4627686399372</v>
@@ -22528,7 +22528,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J2" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -22552,28 +22552,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
-        <v>86.7522584701349</v>
+        <v>127.4161621813053</v>
       </c>
       <c r="W2" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X2" t="n">
-        <v>257.4433377699955</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y2" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="3">
@@ -22586,25 +22586,25 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D3" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -22640,19 +22640,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U3" t="n">
-        <v>176.67144153744</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W3" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="4">
@@ -22683,7 +22683,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I4" t="n">
-        <v>140.6136200195524</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -22704,7 +22704,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
         <v>86.16204325169439</v>
@@ -22747,13 +22747,13 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D5" t="n">
-        <v>354.683041620683</v>
+        <v>123.8085460246003</v>
       </c>
       <c r="E5" t="n">
-        <v>143.1692977759564</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F5" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G5" t="n">
         <v>415.302737515135</v>
@@ -22786,7 +22786,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
         <v>149.8691179411497</v>
@@ -22795,7 +22795,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U5" t="n">
         <v>251.3456529078365</v>
@@ -22823,28 +22823,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -22871,19 +22871,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>136.3170690290597</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W6" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X6" t="n">
         <v>205.7729852034775</v>
@@ -22920,13 +22920,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I7" t="n">
-        <v>155.4504749272583</v>
+        <v>137.8921792844459</v>
       </c>
       <c r="J7" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -22941,13 +22941,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R7" t="n">
-        <v>132.9899077786024</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S7" t="n">
         <v>224.0165980369723</v>
@@ -22990,19 +22990,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>406.8760457417114</v>
+        <v>176.0015501456288</v>
       </c>
       <c r="G8" t="n">
-        <v>300.3857138274809</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H8" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,13 +23023,13 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
         <v>223.0958495641314</v>
@@ -23057,13 +23057,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>27.31724297911936</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>21.08647536425178</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -23160,10 +23160,10 @@
         <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>71.32518834398849</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23184,7 +23184,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>132.9899077786024</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23227,7 +23227,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
         <v>415.302737515135</v>
@@ -23236,7 +23236,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
-        <v>20.14307813956319</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23260,19 +23260,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23281,10 +23281,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X11" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y11" t="n">
-        <v>145.2379386560536</v>
+        <v>346.4650733326886</v>
       </c>
     </row>
     <row r="12">
@@ -23297,25 +23297,25 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -23342,13 +23342,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>42.18625957587292</v>
       </c>
       <c r="U12" t="n">
         <v>225.9413820809748</v>
@@ -23360,10 +23360,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
-        <v>120.5147096390046</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="13">
@@ -23394,13 +23394,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>22.26350734189026</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
-        <v>93.35918011667277</v>
+        <v>71.32518834398849</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23415,10 +23415,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>177.2933913771695</v>
@@ -23452,16 +23452,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C14" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D14" t="n">
-        <v>142.4102416206593</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E14" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F14" t="n">
         <v>406.8760457417114</v>
@@ -23473,10 +23473,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I14" t="n">
-        <v>210.4758895704059</v>
+        <v>10.13979328157632</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23509,7 +23509,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23518,10 +23518,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X14" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y14" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="15">
@@ -23531,10 +23531,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>57.17115494522281</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
         <v>147.4450655646388</v>
@@ -23552,7 +23552,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>89.39663285141508</v>
+        <v>85.5626750829564</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="16">
@@ -23631,13 +23631,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>115.622687458563</v>
+        <v>140.6136200195524</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>86.16204325169439</v>
@@ -23698,19 +23698,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E17" t="n">
-        <v>179.6482692868066</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H17" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -23740,10 +23740,10 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>199.2828334142264</v>
       </c>
       <c r="U17" t="n">
         <v>251.3456529078365</v>
@@ -23768,22 +23768,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>112.2354442364965</v>
@@ -23819,7 +23819,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
         <v>200.1647286948216</v>
@@ -23831,13 +23831,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>44.63024763892324</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>24.39050272738672</v>
       </c>
     </row>
     <row r="19">
@@ -23904,7 +23904,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23913,7 +23913,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366913</v>
       </c>
       <c r="Y19" t="n">
         <v>218.5846533520948</v>
@@ -23926,25 +23926,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>170.4484560200386</v>
       </c>
       <c r="C20" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D20" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E20" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>127.2020021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
@@ -24008,7 +24008,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -24017,10 +24017,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>135.1146339314746</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>112.2354442364965</v>
@@ -24059,19 +24059,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>79.02732540226935</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
         <v>205.6826957773044</v>
@@ -24144,10 +24144,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V22" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W22" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
         <v>225.7096553890372</v>
@@ -24172,16 +24172,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>381.9303700722618</v>
+        <v>169.6449844288197</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
         <v>210.4758895704059</v>
@@ -24208,7 +24208,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214472547</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
@@ -24217,10 +24217,10 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>10.8230495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,7 +24257,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24293,25 +24293,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>101.9362516896722</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>121.666639234045</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -24327,7 +24327,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D25" t="n">
-        <v>15.42850543284433</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E25" t="n">
         <v>146.4339626465692</v>
@@ -24378,7 +24378,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24409,16 +24409,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G26" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H26" t="n">
-        <v>339.4748021157671</v>
+        <v>137.1801156868699</v>
       </c>
       <c r="I26" t="n">
         <v>210.4758895704059</v>
@@ -24457,16 +24457,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>49.06355212238131</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
         <v>386.2379386560536</v>
@@ -24479,10 +24479,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>142.9506534221933</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
@@ -24494,7 +24494,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>66.49556456893617</v>
       </c>
       <c r="H27" t="n">
         <v>112.2354442364965</v>
@@ -24527,25 +24527,25 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -24624,10 +24624,10 @@
         <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
-        <v>92.52268780366913</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y28" t="n">
-        <v>218.5846533520948</v>
+        <v>85.3976857667268</v>
       </c>
     </row>
     <row r="29">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>170.4610416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
@@ -24649,10 +24649,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24703,10 +24703,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>173.9525530126115</v>
       </c>
     </row>
     <row r="30">
@@ -24716,10 +24716,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24731,7 +24731,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>132.8184203449134</v>
+        <v>52.87046265839953</v>
       </c>
       <c r="H30" t="n">
         <v>112.2354442364965</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24886,13 +24886,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H32" t="n">
-        <v>127.202002115648</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
@@ -24934,16 +24934,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>327.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y32" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24965,10 +24965,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>45.0315933124527</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -25001,7 +25001,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -25013,10 +25013,10 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>147.0120521899792</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
@@ -25044,7 +25044,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
-        <v>12.23408043756322</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
         <v>167.9909793584588</v>
@@ -25089,7 +25089,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25111,7 +25111,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C35" t="n">
         <v>365.2728917710076</v>
@@ -25129,7 +25129,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>137.1801156868699</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25171,16 +25171,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>125.4701576846797</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>108.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X35" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="36">
@@ -25247,19 +25247,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>175.924850211182</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>175.8836868124217</v>
       </c>
     </row>
     <row r="37">
@@ -25317,7 +25317,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>44.10642379180146</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25335,7 +25335,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366916</v>
       </c>
       <c r="Y37" t="n">
         <v>218.5846533520948</v>
@@ -25351,19 +25351,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>162.9907909855524</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>195.0896117727101</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
@@ -25402,10 +25402,10 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25414,10 +25414,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X38" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="39">
@@ -25427,13 +25427,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -25490,13 +25490,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X39" t="n">
-        <v>120.5147096390045</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>47.49529702573832</v>
       </c>
     </row>
     <row r="40">
@@ -25512,7 +25512,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D40" t="n">
-        <v>15.42850543284433</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E40" t="n">
         <v>146.4339626465692</v>
@@ -25554,7 +25554,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S40" t="n">
         <v>224.0165980369723</v>
@@ -25585,31 +25585,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C41" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>169.6449844288197</v>
       </c>
       <c r="F41" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G41" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H41" t="n">
-        <v>149.1419906849244</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25667,7 +25667,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
         <v>147.4450655646388</v>
@@ -25688,7 +25688,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25721,19 +25721,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>143.6069553222781</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>175.8836868124217</v>
       </c>
     </row>
     <row r="43">
@@ -25785,13 +25785,13 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>132.9899077786024</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S43" t="n">
         <v>224.0165980369723</v>
@@ -25822,22 +25822,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C44" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D44" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E44" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F44" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G44" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H44" t="n">
         <v>339.4748021157671</v>
@@ -25867,19 +25867,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
-        <v>209.0200695861083</v>
+        <v>6.725383157348119</v>
       </c>
       <c r="T44" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U44" t="n">
-        <v>39.07285290783653</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25891,7 +25891,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y44" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="45">
@@ -25901,7 +25901,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>172.7084989883157</v>
@@ -25910,13 +25910,13 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E45" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>112.2354442364965</v>
@@ -25925,7 +25925,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -25958,19 +25958,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>83.4650136924833</v>
       </c>
       <c r="Y45" t="n">
-        <v>175.924850211182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -25986,7 +25986,7 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D46" t="n">
-        <v>148.6154730182124</v>
+        <v>15.42850543284436</v>
       </c>
       <c r="E46" t="n">
         <v>146.4339626465692</v>
@@ -26037,7 +26037,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>473548.276336042</v>
+        <v>473557.9167142977</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>473548.2763360422</v>
+        <v>473557.9167142977</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>473548.2763360423</v>
+        <v>473557.9167142977</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>473548.2763360422</v>
+        <v>473557.9167142977</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>473548.2763360449</v>
+        <v>473557.9167142975</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>473548.2763360422</v>
+        <v>473557.9167142977</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>473548.2763360423</v>
+        <v>473557.9167142975</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>473548.2763360504</v>
+        <v>473557.9167142974</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>473548.2763360422</v>
+        <v>473557.9167142975</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>473548.276336042</v>
+        <v>473557.9167142975</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>473548.2763360555</v>
+        <v>473557.9167142975</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>473548.2763360422</v>
+        <v>473557.9167142975</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>473548.2763360423</v>
+        <v>473557.9167142977</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>473548.2763360423</v>
+        <v>473557.9167142977</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>473548.2763360575</v>
+        <v>473557.9167142977</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="C2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="D2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="E2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="F2" t="n">
-        <v>108002.2384626066</v>
+        <v>108004.437145366</v>
       </c>
       <c r="G2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.4371453661</v>
       </c>
       <c r="H2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="I2" t="n">
-        <v>108002.2384626079</v>
+        <v>108004.437145366</v>
       </c>
       <c r="J2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="K2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="L2" t="n">
-        <v>108002.2384626091</v>
+        <v>108004.437145366</v>
       </c>
       <c r="M2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="N2" t="n">
-        <v>108002.238462606</v>
+        <v>108004.437145366</v>
       </c>
       <c r="O2" t="n">
-        <v>108002.2384626061</v>
+        <v>108004.437145366</v>
       </c>
       <c r="P2" t="n">
-        <v>108002.2384626096</v>
+        <v>108004.437145366</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910623</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="C4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="E4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="F4" t="n">
-        <v>179.5221438966188</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="G4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966247</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>179.5221438966304</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="M4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="N4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="O4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="P4" t="n">
-        <v>179.5221438966326</v>
+        <v>179.5324977039669</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-21222.32668129058</v>
+        <v>-21225.79564764731</v>
       </c>
       <c r="C6" t="n">
-        <v>59542.31631870943</v>
+        <v>59543.63588390039</v>
       </c>
       <c r="D6" t="n">
-        <v>59542.31631870942</v>
+        <v>59543.63588390039</v>
       </c>
       <c r="E6" t="n">
-        <v>93169.91631870942</v>
+        <v>93171.2358839004</v>
       </c>
       <c r="F6" t="n">
-        <v>93169.91631871001</v>
+        <v>93171.2358839004</v>
       </c>
       <c r="G6" t="n">
-        <v>93169.91631870941</v>
+        <v>93171.23588390042</v>
       </c>
       <c r="H6" t="n">
-        <v>93169.91631870937</v>
+        <v>93171.23588390037</v>
       </c>
       <c r="I6" t="n">
-        <v>93169.91631871123</v>
+        <v>93171.2358839004</v>
       </c>
       <c r="J6" t="n">
-        <v>30113.71231870941</v>
+        <v>30111.29328479415</v>
       </c>
       <c r="K6" t="n">
-        <v>93169.91631870938</v>
+        <v>93171.23588390039</v>
       </c>
       <c r="L6" t="n">
-        <v>93169.91631871246</v>
+        <v>93171.23588390039</v>
       </c>
       <c r="M6" t="n">
-        <v>93169.91631870941</v>
+        <v>93171.23588390039</v>
       </c>
       <c r="N6" t="n">
-        <v>93169.91631870939</v>
+        <v>93171.23588390037</v>
       </c>
       <c r="O6" t="n">
-        <v>93169.91631870945</v>
+        <v>93171.2358839004</v>
       </c>
       <c r="P6" t="n">
-        <v>93169.91631871293</v>
+        <v>93171.23588390039</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,7 +26895,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26907,34 +26907,34 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34629,7 +34629,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P2" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34699,13 +34699,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>91.05495334897203</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="P3" t="n">
         <v>184.4883612256069</v>
@@ -34851,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L5" t="n">
         <v>181.8947995804632</v>
@@ -34860,7 +34860,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N5" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O5" t="n">
         <v>150.7019698410586</v>
@@ -34936,19 +34936,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M6" t="n">
-        <v>241</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N6" t="n">
-        <v>169.8645014752148</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P6" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -35088,7 +35088,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L8" t="n">
         <v>181.8947995804632</v>
@@ -35097,7 +35097,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N8" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O8" t="n">
         <v>150.7019698410586</v>
@@ -35170,16 +35170,16 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M9" t="n">
-        <v>241</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="N9" t="n">
-        <v>91.05495334897201</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P9" t="n">
         <v>184.4883612256069</v>
@@ -35325,7 +35325,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L11" t="n">
         <v>181.8947995804632</v>
@@ -35334,7 +35334,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N11" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O11" t="n">
         <v>150.7019698410586</v>
@@ -35404,22 +35404,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M12" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O12" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P12" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>70.09551364982758</v>
@@ -35577,7 +35577,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P14" t="n">
-        <v>90.50913423399129</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35647,19 +35647,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M15" t="n">
-        <v>99.76898782538704</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P15" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q15" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35799,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L17" t="n">
         <v>181.8947995804632</v>
@@ -35884,16 +35884,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M18" t="n">
-        <v>226.3927858636066</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>169.9091475161414</v>
       </c>
       <c r="P18" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>70.09551364982758</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,19 +36121,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>55.48829951343436</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P23" t="n">
-        <v>90.5091342340409</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N24" t="n">
-        <v>113.3528627008217</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36589,19 +36589,19 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>169.8645014752148</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36832,16 +36832,16 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
-        <v>161.1671126127986</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
         <v>70.09551364982758</v>
@@ -36999,7 +36999,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>90.50913423408866</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,19 +37063,19 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>161.1504669987997</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>241</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="N33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
@@ -37221,7 +37221,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>55.48829951343433</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4883612256069</v>
+        <v>161.1808241620674</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37464,7 +37464,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37543,13 +37543,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>55.48829951343433</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N39" t="n">
-        <v>241</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
@@ -37698,7 +37698,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
         <v>219.1673002655598</v>
@@ -37774,25 +37774,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>91.05495334897203</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="N42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O42" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37947,7 +37947,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P44" t="n">
-        <v>90.50913423410704</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38011,19 +38011,19 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M45" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>55.51629994036219</v>
       </c>
       <c r="P45" t="n">
         <v>184.4883612256069</v>
